--- a/testFile/case/AccessExcel.xlsx
+++ b/testFile/case/AccessExcel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17475" windowHeight="8062" activeTab="4"/>
+    <workbookView windowWidth="20317" windowHeight="9727" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="access" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,20 @@
     <sheet name="role" sheetId="4" r:id="rId4"/>
     <sheet name="sysorg" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -633,20 +646,20 @@
   </si>
   <si>
     <t>{
-  "execDate": "2023-10-10",
+  "execDate": "2023-12-26",
   "routeId": "",
   "shiftNum": "",
-  "busNumber": "1-9694",
+  "busNumber": "1-9849",
   "attendType": "ALL_ATTEND",
-  "siteId": 14,
+  "siteId": 1,
   "siteId2": "",
-  "planOnTime": "2023-10-10 10:00:00",
-  "onWorkTime1": "2023-10-10 12:00:00",
+  "planOnTime": "2023-12-26 16:50:02",
+  "onWorkTime1": "2023-12-26 16:50:04",
   "endTime": "",
   "driverJobId": "90179035",
   "remark": "测试",
-  "type": "SAN_BAO",
-  "siteName": "九和路停车场",
+  "type": "OTHER",
+  "siteName": "阮家桥公交停车场",
   "canSubmit": ""
 }</t>
   </si>
@@ -859,12 +872,12 @@
   </si>
   <si>
     <t>{
-  "id": 30355,
-  "routeName": "187路",
+  "id": 30315,
+  "routeName": "85路",
   "operateStatus": 1,
-  "operateTime": "03:50:01",
+  "operateTime": "03:50:00",
   "unoperateStatus": 1,
-  "unoperateTime": "03:50:01"
+  "unoperateTime": "03:50:00"
 }</t>
   </si>
   <si>
@@ -1128,7 +1141,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
